--- a/data/gravel/Trek Checkout 2025.xlsx
+++ b/data/gravel/Trek Checkout 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16897C02-317C-184D-BF6D-062A9082C235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AD6619-302D-6048-8802-2933327421E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9620" yWindow="1720" windowWidth="30540" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="1880" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="147">
   <si>
     <t>brand</t>
   </si>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t>semi-integrated</t>
+  </si>
+  <si>
+    <t>20% sag</t>
   </si>
 </sst>
 </file>
@@ -1657,8 +1660,13 @@
       <c r="G24">
         <v>475</v>
       </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
+      <c r="I24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" s="3">
+        <f>475 - 0.2*60</f>
+        <v>463</v>
+      </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -1984,6 +1992,9 @@
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>59</v>
+      </c>
+      <c r="B42">
+        <v>60</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="2" t="s">

--- a/data/gravel/Trek Checkout 2025.xlsx
+++ b/data/gravel/Trek Checkout 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AD6619-302D-6048-8802-2933327421E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E8B164-3265-754E-ACDB-9B903B77ED8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="1880" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32320" yWindow="-23620" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="148">
   <si>
     <t>brand</t>
   </si>
@@ -474,6 +474,9 @@
   </si>
   <si>
     <t>20% sag</t>
+  </si>
+  <si>
+    <t>https://media.trekbikes.com/image/upload/w_1920,h_1440,c_pad,f_auto,fl_progressive:semi,q_auto/CheckoutSL7AXS-26-57828-B-Primary</t>
   </si>
 </sst>
 </file>
@@ -882,6 +885,11 @@
         <v>97</v>
       </c>
     </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>147</v>
+      </c>
+    </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/Trek Checkout 2025.xlsx
+++ b/data/gravel/Trek Checkout 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E8B164-3265-754E-ACDB-9B903B77ED8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA94583D-6E03-8746-9500-38FF9FB5A3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32320" yWindow="-23620" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="150">
   <si>
     <t>brand</t>
   </si>
@@ -477,6 +477,12 @@
   </si>
   <si>
     <t>https://media.trekbikes.com/image/upload/w_1920,h_1440,c_pad,f_auto,fl_progressive:semi,q_auto/CheckoutSL7AXS-26-57828-B-Primary</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Waterloo, Wisconsin, USA</t>
   </si>
 </sst>
 </file>
@@ -839,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V71"/>
+  <dimension ref="A1:V72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2207,6 +2213,14 @@
       </c>
       <c r="B71" s="1" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Trek Checkout 2025.xlsx
+++ b/data/gravel/Trek Checkout 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA94583D-6E03-8746-9500-38FF9FB5A3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1369E4B-9BFD-6A48-B4C7-FC36D987EEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="156">
   <si>
     <t>brand</t>
   </si>
@@ -483,6 +483,24 @@
   </si>
   <si>
     <t>Waterloo, Wisconsin, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -845,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V72"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2057,169 +2075,199 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>66</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>68</v>
-      </c>
-      <c r="B50">
-        <v>31.6</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52">
-        <v>38</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>68</v>
+      </c>
+      <c r="B56">
+        <v>31.6</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>74</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>76</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B58">
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>79</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>80</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>82</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>74</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>85</v>
-      </c>
-      <c r="B66" s="1"/>
+        <v>79</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>86</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>55</v>
+        <v>80</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B68">
-        <v>3699.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B69">
-        <v>5799.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>90</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>85</v>
+      </c>
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>86</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>87</v>
+      </c>
+      <c r="B74">
+        <v>3699.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75">
+        <v>5799.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>90</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>148</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>149</v>
       </c>
     </row>

--- a/data/gravel/Trek Checkout 2025.xlsx
+++ b/data/gravel/Trek Checkout 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1369E4B-9BFD-6A48-B4C7-FC36D987EEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237C516F-558F-8D4C-91EA-AC02358FB4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="156">
   <si>
     <t>brand</t>
   </si>
@@ -2219,6 +2219,9 @@
       <c r="A71" t="s">
         <v>84</v>
       </c>
+      <c r="B71" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">

--- a/data/gravel/Trek Checkout 2025.xlsx
+++ b/data/gravel/Trek Checkout 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237C516F-558F-8D4C-91EA-AC02358FB4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE024E0E-C259-CF47-8E28-8E9F912CBDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="158">
   <si>
     <t>brand</t>
   </si>
@@ -467,9 +467,6 @@
     <t>36" - 37"</t>
   </si>
   <si>
-    <t>a8:g31</t>
-  </si>
-  <si>
     <t>semi-integrated</t>
   </si>
   <si>
@@ -501,6 +498,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:g33</t>
   </si>
 </sst>
 </file>
@@ -863,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V78"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -911,7 +917,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -919,7 +925,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -1693,7 +1699,7 @@
         <v>475</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J24" s="3">
         <f>475 - 0.2*60</f>
@@ -1705,11 +1711,23 @@
       <c r="N24" s="3"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
+      <c r="A25" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25">
+        <v>60</v>
+      </c>
+      <c r="D25">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>60</v>
+      </c>
+      <c r="F25">
+        <v>60</v>
+      </c>
+      <c r="G25">
+        <v>60</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
@@ -1719,26 +1737,8 @@
       <c r="N25" s="3"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26">
-        <v>60</v>
-      </c>
-      <c r="D26">
-        <v>60</v>
-      </c>
-      <c r="E26">
-        <v>70</v>
-      </c>
-      <c r="F26">
-        <v>70</v>
-      </c>
-      <c r="G26">
-        <v>80</v>
+      <c r="A26" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
@@ -1749,10 +1749,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
@@ -1763,25 +1763,25 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C28">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D28">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E28">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F28">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G28">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
@@ -1792,25 +1792,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29">
-        <v>56</v>
-      </c>
-      <c r="D29">
-        <v>56</v>
-      </c>
-      <c r="E29">
-        <v>56</v>
-      </c>
-      <c r="F29">
-        <v>56</v>
-      </c>
-      <c r="G29">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
@@ -1821,25 +1806,25 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C30">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="D30">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="E30">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="F30">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G30">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="3"/>
@@ -1850,388 +1835,432 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31">
+        <v>56</v>
+      </c>
+      <c r="D31">
+        <v>56</v>
+      </c>
+      <c r="E31">
+        <v>56</v>
+      </c>
+      <c r="F31">
+        <v>56</v>
+      </c>
+      <c r="G31">
+        <v>56</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32">
+        <v>158</v>
+      </c>
+      <c r="D32">
+        <v>164</v>
+      </c>
+      <c r="E32">
+        <v>177</v>
+      </c>
+      <c r="F32">
+        <v>188</v>
+      </c>
+      <c r="G32">
+        <v>194</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>50</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>50</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <v>164</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>177</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>188</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <v>194</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C32" s="5" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C34" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>51</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B35" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>91</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>92</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>114</v>
+        <v>93</v>
+      </c>
+      <c r="B37" t="s">
+        <v>94</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" t="s">
-        <v>55</v>
+        <v>95</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>53</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B40" t="s">
+        <v>55</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44">
+        <v>60</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>60</v>
       </c>
-      <c r="B43">
+      <c r="B45">
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>62</v>
       </c>
-      <c r="B45">
+      <c r="B47">
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>63</v>
       </c>
-      <c r="B46">
+      <c r="B48">
         <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-      <c r="B47">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>151</v>
+        <v>64</v>
+      </c>
+      <c r="B49">
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>68</v>
-      </c>
-      <c r="B56">
-        <v>31.6</v>
+        <v>65</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B58">
-        <v>38</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="B60">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>74</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>80</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>81</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
+        <v>79</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>84</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>55</v>
+        <v>82</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>85</v>
-      </c>
-      <c r="B72" s="1"/>
+        <v>83</v>
+      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>55</v>
@@ -2239,48 +2268,62 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>87</v>
-      </c>
-      <c r="B74">
-        <v>3699.99</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>88</v>
-      </c>
-      <c r="B75">
-        <v>5799.99</v>
+        <v>86</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>87</v>
+      </c>
+      <c r="B76">
+        <v>3699.99</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>90</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
+      </c>
+      <c r="B77">
+        <v>5799.99</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>90</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>147</v>
+      </c>
+      <c r="B80" t="s">
         <v>148</v>
-      </c>
-      <c r="B78" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C33:C34"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="C37:C38"/>
     <mergeCell ref="C39:C40"/>
     <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
